--- a/testakten/startup-gruender-schnittflug-berlin/51_Auslagen_und_Liquiditaetsplanung.xlsx
+++ b/testakten/startup-gruender-schnittflug-berlin/51_Auslagen_und_Liquiditaetsplanung.xlsx
@@ -2,14 +2,17 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Liquidität" sheetId="1" r:id="Rd2c4b708f1af4fd8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Auslagen" sheetId="2" r:id="Rfdccad0b39a94e0b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Annahmen" sheetId="3" r:id="Rc0a3b8a5ff2e4c48"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Liquidität" sheetId="1" r:id="R27b6991191c44efa"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Auslagen" sheetId="2" r:id="R4ee9d07a01db486e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Annahmen" sheetId="3" r:id="R393f0ae342bb4767"/>
   </x:sheets>
   <x:definedNames>
     <x:definedName name="_xlnm.Print_Area" localSheetId="0">'Liquidität'!$B$2:$H$36</x:definedName>
+    <x:definedName name="_xlnm.Print_Titles" localSheetId="0">'Liquidität'!$6:$6</x:definedName>
     <x:definedName name="_xlnm.Print_Area" localSheetId="1">'Auslagen'!$B$2:$L$33</x:definedName>
+    <x:definedName name="_xlnm.Print_Titles" localSheetId="1">'Auslagen'!$6:$6</x:definedName>
     <x:definedName name="_xlnm.Print_Area" localSheetId="2">'Annahmen'!$B$2:$H$43</x:definedName>
+    <x:definedName name="_xlnm.Print_Titles" localSheetId="2">'Annahmen'!$6:$6</x:definedName>
   </x:definedNames>
 </x:workbook>
 </file>
